--- a/spec/fixtures/files/import_assessment_questions/invalid_headers.xlsx
+++ b/spec/fixtures/files/import_assessment_questions/invalid_headers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rohanpujari/tte/psychometrics/spec/fixtures/files/import_assessment_question/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rohan-pujari/tte/psychometrics/spec/fixtures/files/import_assessment_questions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C089B398-4A6C-4945-87FF-AC284DEA06B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8DDC87-A0A8-0F4E-9479-47C8E02E5328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="35120" windowHeight="22500" xr2:uid="{076B2D0F-1935-5E46-9497-2286E1A2EE28}"/>
+    <workbookView xWindow="0" yWindow="1100" windowWidth="32020" windowHeight="22260" xr2:uid="{076B2D0F-1935-5E46-9497-2286E1A2EE28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
   <si>
     <t>Q1</t>
   </si>
@@ -74,9 +74,6 @@
     <t>answersType</t>
   </si>
   <si>
-    <t>Grit</t>
-  </si>
-  <si>
     <t>Please enter your last name</t>
   </si>
   <si>
@@ -95,13 +92,17 @@
     <t>SingleLine</t>
   </si>
   <si>
-    <t>Accountability</t>
-  </si>
-  <si>
     <t>scalePointsTexts</t>
   </si>
   <si>
     <t>Blocks</t>
+  </si>
+  <si>
+    <t>Factors</t>
+  </si>
+  <si>
+    <t>Accountability: 1,2
+Grit: 1, 2</t>
   </si>
 </sst>
 </file>
@@ -143,8 +144,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -479,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2760F84-0E72-1247-B859-B08C7CC9D341}">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
@@ -497,9 +501,9 @@
     <col min="17" max="17" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
@@ -541,16 +545,13 @@
         <v>6</v>
       </c>
       <c r="O1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P1" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -579,31 +580,28 @@
         <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M2" t="s">
         <v>9</v>
       </c>
       <c r="N2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O2" t="s">
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -611,16 +609,19 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O3" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
